--- a/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Triphammer_20260220.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Triphammer_20260220.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,48 @@
         <v>86.52</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10G108024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bag - Poly (10x8x24, 1mil)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="E7" t="n">
+        <v>74.73999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LKC1624F</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lid - Parfait (16/24oz)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>56.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
